--- a/artfynd/A 38488-2025 artfynd.xlsx
+++ b/artfynd/A 38488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119628807</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119628806</v>
+        <v>119628805</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613367</v>
+        <v>613322</v>
       </c>
       <c r="R3" t="n">
-        <v>6953646</v>
+        <v>6953696</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119628808</v>
+        <v>119628802</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613365</v>
+        <v>613320</v>
       </c>
       <c r="R4" t="n">
-        <v>6953576</v>
+        <v>6953727</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119628809</v>
+        <v>119628808</v>
       </c>
       <c r="B5" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,16 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1062,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613457</v>
+        <v>613365</v>
       </c>
       <c r="R5" t="n">
-        <v>6953390</v>
+        <v>6953576</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,6 +1116,450 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119628800</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Uddefors, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613358</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6953736</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119628806</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Uddefors, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>613367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6953646</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119628804</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Uddefors, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>613326</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6953715</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119628809</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Uddefors, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>613457</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6953390</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38488-2025 artfynd.xlsx
+++ b/artfynd/A 38488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628807</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628802</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628808</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628800</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628806</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,8 +1600,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>